--- a/Eventos.xlsx
+++ b/Eventos.xlsx
@@ -11,9 +11,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
-  <si>
-    <t>EVENTO 1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="16">
+  <si>
+    <t>RAMPA.MVD</t>
+  </si>
+  <si>
+    <t>12.00 H</t>
+  </si>
+  <si>
+    <t>SUBÍ A LO QUE ESTÁ PASANDO</t>
+  </si>
+  <si>
+    <t>MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>RAVE</t>
+  </si>
+  <si>
+    <t>EVENTO 2</t>
   </si>
   <si>
     <t>23.00 H</t>
@@ -23,12 +38,6 @@
   </si>
   <si>
     <t>DOMINGO</t>
-  </si>
-  <si>
-    <t>RAVE</t>
-  </si>
-  <si>
-    <t>EVENTO 2</t>
   </si>
   <si>
     <t>EVENTO 3</t>
@@ -327,7 +336,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>45886.0</v>
+        <v>45889.0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -350,13 +359,13 @@
         <v>45886.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
@@ -364,19 +373,19 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4">
         <v>45886.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>4</v>
@@ -384,19 +393,19 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4">
         <v>45886.0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>4</v>
@@ -404,19 +413,19 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4">
         <v>45886.0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>4</v>
@@ -424,19 +433,19 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4">
         <v>45886.0</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>4</v>
@@ -444,19 +453,19 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4">
         <v>45886.0</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>4</v>
@@ -464,19 +473,19 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4">
         <v>45886.0</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>4</v>
@@ -484,19 +493,19 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4">
         <v>45886.0</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>4</v>

--- a/Eventos.xlsx
+++ b/Eventos.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Eventos Aprobados" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Eventos Pendientes" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>RAMPA.MVD</t>
   </si>
@@ -28,45 +29,34 @@
     <t>RAVE</t>
   </si>
   <si>
-    <t>EVENTO 2</t>
-  </si>
-  <si>
-    <t>23.00 H</t>
-  </si>
-  <si>
-    <t>FLHEZ, FEFIO</t>
+    <t>Test Manual</t>
+  </si>
+  <si>
+    <t>hahfhadhf</t>
   </si>
   <si>
     <t>DOMINGO</t>
   </si>
   <si>
-    <t>EVENTO 3</t>
-  </si>
-  <si>
-    <t>EVENTO 4</t>
-  </si>
-  <si>
-    <t>EVENTO 5</t>
-  </si>
-  <si>
-    <t>EVENTO 6</t>
-  </si>
-  <si>
-    <t>EVENTO 7</t>
-  </si>
-  <si>
-    <t>EVENTO 8</t>
-  </si>
-  <si>
-    <t>EVENTO 9</t>
+    <t>PENDIENTE</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>Test Location</t>
+  </si>
+  <si>
+    <t>Test Manual 1755807075718</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd.mm.yy"/>
+    <numFmt numFmtId="165" formatCode="d/m/yyyy, h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -99,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -117,6 +107,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -127,6 +123,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -330,13 +330,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="7" max="7" width="17.5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>45889.0</v>
+        <v>45890.0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -349,6 +352,119 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2"/>
+      <c r="C10" s="6"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2"/>
+      <c r="C12" s="6"/>
+      <c r="G12" s="7"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="7" max="7" width="14.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C1" s="6">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="7">
+        <v>45890.495104166665</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
@@ -356,159 +472,51 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>45886.0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>45893.0</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.9166666666666666</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="7">
+        <v>45890.70349537037</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4">
-        <v>45886.0</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="7">
+        <v>45890.716157407405</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4">
-        <v>45886.0</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4">
-        <v>45886.0</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="4">
-        <v>45886.0</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="4">
-        <v>45886.0</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="4">
-        <v>45886.0</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="4">
-        <v>45886.0</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Eventos.xlsx
+++ b/Eventos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="18">
   <si>
     <t>RAMPA.MVD</t>
   </si>
@@ -29,25 +29,43 @@
     <t>RAVE</t>
   </si>
   <si>
+    <t>Test Manual 1755809275251</t>
+  </si>
+  <si>
+    <t>Test Location</t>
+  </si>
+  <si>
+    <t>DOMINGO</t>
+  </si>
+  <si>
+    <t>PENDIENTE</t>
+  </si>
+  <si>
     <t>Test Manual</t>
   </si>
   <si>
     <t>hahfhadhf</t>
   </si>
   <si>
-    <t>DOMINGO</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-  <si>
     <t>@</t>
   </si>
   <si>
-    <t>Test Location</t>
-  </si>
-  <si>
     <t>Test Manual 1755807075718</t>
+  </si>
+  <si>
+    <t>Test Manual 1755807918493</t>
+  </si>
+  <si>
+    <t>Test Manual 1755808547631</t>
+  </si>
+  <si>
+    <t>Test Manual 1755809083471</t>
+  </si>
+  <si>
+    <t>Test Manual 1755866067265</t>
+  </si>
+  <si>
+    <t>Test Manual 1755866083405</t>
   </si>
 </sst>
 </file>
@@ -99,6 +117,12 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
@@ -107,12 +131,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -355,73 +373,96 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="2"/>
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4">
+        <v>45890.7416087963</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10">
       <c r="B10" s="2"/>
-      <c r="C10" s="6"/>
-      <c r="G10" s="7"/>
+      <c r="C10" s="3"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="2"/>
-      <c r="C12" s="6"/>
-      <c r="G12" s="7"/>
+      <c r="C12" s="3"/>
+      <c r="G12" s="4"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -440,16 +481,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2">
         <v>45893.0</v>
       </c>
-      <c r="C1" s="6">
+      <c r="C1" s="3">
         <v>0.9166666666666666</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -457,28 +498,28 @@
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="7">
+      <c r="G1" s="4">
         <v>45890.495104166665</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>45893.0</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="3">
         <v>0.9166666666666666</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
@@ -486,7 +527,7 @@
       <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="4">
         <v>45890.70349537037</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -495,16 +536,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2">
         <v>45893.0</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>0.9166666666666666</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -512,10 +553,166 @@
       <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="4">
         <v>45890.716157407405</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="4">
+        <v>45890.725902777776</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4">
+        <v>45890.73318287037</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="4">
+        <v>45890.739386574074</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="4">
+        <v>45890.7416087963</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4">
+        <v>45891.39892361111</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4">
+        <v>45891.39912037037</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Eventos.xlsx
+++ b/Eventos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>RAMPA.MVD</t>
   </si>
@@ -23,49 +23,28 @@
     <t>SUBÍ A LO QUE ESTÁ PASANDO</t>
   </si>
   <si>
+    <t>RAVE</t>
+  </si>
+  <si>
     <t>MIÉRCOLES</t>
   </si>
   <si>
-    <t>RAVE</t>
-  </si>
-  <si>
-    <t>Test Manual 1755809275251</t>
-  </si>
-  <si>
-    <t>Test Location</t>
-  </si>
-  <si>
-    <t>DOMINGO</t>
+    <t>I</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>AIRE LIBRE</t>
+  </si>
+  <si>
+    <t>JUEVES</t>
   </si>
   <si>
     <t>PENDIENTE</t>
   </si>
   <si>
-    <t>Test Manual</t>
-  </si>
-  <si>
-    <t>hahfhadhf</t>
-  </si>
-  <si>
-    <t>@</t>
-  </si>
-  <si>
-    <t>Test Manual 1755807075718</t>
-  </si>
-  <si>
-    <t>Test Manual 1755807918493</t>
-  </si>
-  <si>
-    <t>Test Manual 1755808547631</t>
-  </si>
-  <si>
-    <t>Test Manual 1755809083471</t>
-  </si>
-  <si>
-    <t>Test Manual 1755866067265</t>
-  </si>
-  <si>
-    <t>Test Manual 1755866083405</t>
+    <t>MUSICA</t>
   </si>
 </sst>
 </file>
@@ -373,30 +352,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="4">
-        <v>45890.7416087963</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="5"/>
@@ -481,240 +439,121 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45890.0</v>
+      </c>
+      <c r="C1" s="3">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="4">
+        <v>45891.56706018518</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B1" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C1" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="4">
-        <v>45890.495104166665</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45890.0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.5958333333333333</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4">
+        <v>45891.59599537037</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="4">
-        <v>45890.70349537037</v>
-      </c>
-      <c r="H2" s="1" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45897.0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.8173611111111111</v>
+      </c>
+      <c r="D3" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="G3" s="4">
-        <v>45890.716157407405</v>
+        <v>45891.609085648146</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="4">
-        <v>45890.725902777776</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="4">
-        <v>45890.73318287037</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="4">
-        <v>45890.739386574074</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="4">
-        <v>45890.7416087963</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="4">
-        <v>45891.39892361111</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2">
-        <v>45893.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="4">
-        <v>45891.39912037037</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="G11" s="4"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Eventos.xlsx
+++ b/Eventos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>RAMPA.MVD</t>
   </si>
@@ -29,6 +29,18 @@
     <t>MIÉRCOLES</t>
   </si>
   <si>
+    <t>KEY CONFERENCE</t>
+  </si>
+  <si>
+    <t>21.00 H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELTRAN TOMAN | NU ZAU b2b SEPP | MANGLUS </t>
+  </si>
+  <si>
+    <t>DOMINGO</t>
+  </si>
+  <si>
     <t>I</t>
   </si>
   <si>
@@ -45,6 +57,24 @@
   </si>
   <si>
     <t>MUSICA</t>
+  </si>
+  <si>
+    <t>ARTE</t>
+  </si>
+  <si>
+    <t>VIERNES</t>
+  </si>
+  <si>
+    <t>-PPP</t>
+  </si>
+  <si>
+    <t>PPP</t>
+  </si>
+  <si>
+    <t>BAR</t>
+  </si>
+  <si>
+    <t>ert</t>
   </si>
 </sst>
 </file>
@@ -96,20 +126,20 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -352,75 +382,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45893.0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
     </row>
     <row r="10">
       <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="G10" s="4"/>
+      <c r="C10" s="7"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="12">
       <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-      <c r="G12" s="4"/>
+      <c r="C12" s="7"/>
+      <c r="G12" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -439,54 +472,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2">
         <v>45890.0</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="7">
         <v>0.5666666666666667</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="4">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3">
         <v>45891.56706018518</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>45890.0</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="7">
         <v>0.5958333333333333</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="4">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3">
         <v>45891.59599537037</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -496,64 +529,148 @@
       <c r="B3" s="2">
         <v>45897.0</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="7">
         <v>0.8173611111111111</v>
       </c>
       <c r="D3" s="1">
         <v>9.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="4">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3">
         <v>45891.609085648146</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="G4" s="4"/>
+      <c r="A4" s="1">
+        <v>123.0</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45876.0</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="D4" s="1">
+        <v>123.0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3">
+        <v>45891.61225694444</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="G5" s="4"/>
+      <c r="A5" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45870.0</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3">
+        <v>45891.614895833336</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="G6" s="4"/>
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45889.0</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.7847222222222222</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3">
+        <v>45891.61832175926</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="G7" s="4"/>
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45882.0</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.7868055555555555</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3">
+        <v>45891.620717592596</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="G8" s="4"/>
+      <c r="C8" s="7"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9">
       <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="G9" s="4"/>
+      <c r="C9" s="7"/>
+      <c r="G9" s="3"/>
     </row>
     <row r="10">
       <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="G10" s="4"/>
+      <c r="C10" s="7"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11">
       <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="G11" s="4"/>
+      <c r="C11" s="7"/>
+      <c r="G11" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
